--- a/datos_reales.xlsx
+++ b/datos_reales.xlsx
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="88" uniqueCount="88">
+<x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="89" uniqueCount="89">
   <x:si>
     <x:t xml:space="preserve">ID</x:t>
   </x:si>
@@ -289,6 +289,9 @@
   </x:si>
   <x:si>
     <x:t xml:space="preserve">Javier Murillo</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Verónica Torres</x:t>
   </x:si>
 </x:sst>
 </file>
@@ -385,8 +388,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Table1" displayName="Table1" ref="A1:L111" insertRow="1" totalsRowShown="0">
-  <x:autoFilter ref="A1:L111"/>
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Table1" displayName="Table1" ref="A1:L140" insertRow="1" totalsRowShown="0">
+  <x:autoFilter ref="A1:L140"/>
   <x:tableColumns count="12">
     <x:tableColumn id="1" uniqueName="1" name="ID" dataDxfId="0"/>
     <x:tableColumn id="2" uniqueName="2" name="Start time" dataDxfId="3"/>
@@ -4057,11 +4060,881 @@
       <x:c r="K111" s="10" t="s"/>
       <x:c r="L111" s="10" t="s"/>
     </x:row>
+    <x:row r="112" hidden="0">
+      <x:c r="A112">
+        <x:v>127</x:v>
+      </x:c>
+      <x:c r="B112" s="2">
+        <x:v>46223.49422453704</x:v>
+      </x:c>
+      <x:c r="C112" s="2">
+        <x:v>46223.49445601852</x:v>
+      </x:c>
+      <x:c r="D112" s="10" t="s">
+        <x:v>72</x:v>
+      </x:c>
+      <x:c r="E112" s="10" t="s">
+        <x:v>73</x:v>
+      </x:c>
+      <x:c r="F112" s="2"/>
+      <x:c r="G112" s="3">
+        <x:v>46224</x:v>
+      </x:c>
+      <x:c r="H112" s="10" t="s">
+        <x:v>18</x:v>
+      </x:c>
+      <x:c r="I112" s="10" t="s">
+        <x:v>73</x:v>
+      </x:c>
+      <x:c r="J112" s="10" t="s"/>
+      <x:c r="K112" s="10" t="s"/>
+      <x:c r="L112" s="10" t="s"/>
+    </x:row>
+    <x:row r="113" hidden="0">
+      <x:c r="A113">
+        <x:v>128</x:v>
+      </x:c>
+      <x:c r="B113" s="2">
+        <x:v>46223.4946412037</x:v>
+      </x:c>
+      <x:c r="C113" s="2">
+        <x:v>46223.494791666664</x:v>
+      </x:c>
+      <x:c r="D113" s="10" t="s">
+        <x:v>35</x:v>
+      </x:c>
+      <x:c r="E113" s="10" t="s">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="F113" s="2"/>
+      <x:c r="G113" s="3">
+        <x:v>46224</x:v>
+      </x:c>
+      <x:c r="H113" s="10" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="I113" s="10" t="s"/>
+      <x:c r="J113" s="10" t="s"/>
+      <x:c r="K113" s="10" t="s"/>
+      <x:c r="L113" s="10" t="s">
+        <x:v>15</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="114" hidden="0">
+      <x:c r="A114">
+        <x:v>129</x:v>
+      </x:c>
+      <x:c r="B114" s="2">
+        <x:v>46223.49484953703</x:v>
+      </x:c>
+      <x:c r="C114" s="2">
+        <x:v>46223.49506944444</x:v>
+      </x:c>
+      <x:c r="D114" s="10" t="s">
+        <x:v>31</x:v>
+      </x:c>
+      <x:c r="E114" s="10" t="s">
+        <x:v>32</x:v>
+      </x:c>
+      <x:c r="F114" s="2"/>
+      <x:c r="G114" s="3">
+        <x:v>46224</x:v>
+      </x:c>
+      <x:c r="H114" s="10" t="s">
+        <x:v>18</x:v>
+      </x:c>
+      <x:c r="I114" s="10" t="s">
+        <x:v>75</x:v>
+      </x:c>
+      <x:c r="J114" s="10" t="s"/>
+      <x:c r="K114" s="10" t="s"/>
+      <x:c r="L114" s="10" t="s"/>
+    </x:row>
+    <x:row r="115" hidden="0">
+      <x:c r="A115">
+        <x:v>130</x:v>
+      </x:c>
+      <x:c r="B115" s="2">
+        <x:v>46223.49532407407</x:v>
+      </x:c>
+      <x:c r="C115" s="2">
+        <x:v>46223.49556712963</x:v>
+      </x:c>
+      <x:c r="D115" s="10" t="s">
+        <x:v>12</x:v>
+      </x:c>
+      <x:c r="E115" s="10" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="F115" s="2"/>
+      <x:c r="G115" s="3">
+        <x:v>46224</x:v>
+      </x:c>
+      <x:c r="H115" s="10" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="I115" s="10" t="s"/>
+      <x:c r="J115" s="10" t="s"/>
+      <x:c r="K115" s="10" t="s"/>
+      <x:c r="L115" s="10" t="s">
+        <x:v>26</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="116" hidden="0">
+      <x:c r="A116">
+        <x:v>131</x:v>
+      </x:c>
+      <x:c r="B116" s="2">
+        <x:v>46223.49482638889</x:v>
+      </x:c>
+      <x:c r="C116" s="2">
+        <x:v>46223.49592592593</x:v>
+      </x:c>
+      <x:c r="D116" s="10" t="s">
+        <x:v>46</x:v>
+      </x:c>
+      <x:c r="E116" s="10" t="s">
+        <x:v>47</x:v>
+      </x:c>
+      <x:c r="F116" s="2"/>
+      <x:c r="G116" s="3">
+        <x:v>46224</x:v>
+      </x:c>
+      <x:c r="H116" s="10" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="I116" s="10" t="s"/>
+      <x:c r="J116" s="10" t="s"/>
+      <x:c r="K116" s="10" t="s"/>
+      <x:c r="L116" s="10" t="s">
+        <x:v>88</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="117" hidden="0">
+      <x:c r="A117">
+        <x:v>132</x:v>
+      </x:c>
+      <x:c r="B117" s="2">
+        <x:v>46223.49443287037</x:v>
+      </x:c>
+      <x:c r="C117" s="2">
+        <x:v>46223.49674768518</x:v>
+      </x:c>
+      <x:c r="D117" s="10" t="s">
+        <x:v>48</x:v>
+      </x:c>
+      <x:c r="E117" s="10" t="s">
+        <x:v>27</x:v>
+      </x:c>
+      <x:c r="F117" s="2"/>
+      <x:c r="G117" s="3">
+        <x:v>46224</x:v>
+      </x:c>
+      <x:c r="H117" s="10" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="I117" s="10" t="s"/>
+      <x:c r="J117" s="10" t="s"/>
+      <x:c r="K117" s="10" t="s"/>
+      <x:c r="L117" s="10" t="s">
+        <x:v>27</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="118" hidden="0">
+      <x:c r="A118">
+        <x:v>133</x:v>
+      </x:c>
+      <x:c r="B118" s="2">
+        <x:v>46223.49710648148</x:v>
+      </x:c>
+      <x:c r="C118" s="2">
+        <x:v>46223.49728009259</x:v>
+      </x:c>
+      <x:c r="D118" s="10" t="s">
+        <x:v>25</x:v>
+      </x:c>
+      <x:c r="E118" s="10" t="s">
+        <x:v>26</x:v>
+      </x:c>
+      <x:c r="F118" s="2"/>
+      <x:c r="G118" s="3">
+        <x:v>46224</x:v>
+      </x:c>
+      <x:c r="H118" s="10" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="I118" s="10" t="s"/>
+      <x:c r="J118" s="10" t="s"/>
+      <x:c r="K118" s="10" t="s"/>
+      <x:c r="L118" s="10" t="s">
+        <x:v>88</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="119" hidden="0">
+      <x:c r="A119">
+        <x:v>134</x:v>
+      </x:c>
+      <x:c r="B119" s="2">
+        <x:v>46223.49564814815</x:v>
+      </x:c>
+      <x:c r="C119" s="2">
+        <x:v>46223.49743055556</x:v>
+      </x:c>
+      <x:c r="D119" s="10" t="s">
+        <x:v>38</x:v>
+      </x:c>
+      <x:c r="E119" s="10" t="s">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="F119" s="2"/>
+      <x:c r="G119" s="3">
+        <x:v>46224</x:v>
+      </x:c>
+      <x:c r="H119" s="10" t="s">
+        <x:v>18</x:v>
+      </x:c>
+      <x:c r="I119" s="10" t="s">
+        <x:v>19</x:v>
+      </x:c>
+      <x:c r="J119" s="10" t="s"/>
+      <x:c r="K119" s="10" t="s"/>
+      <x:c r="L119" s="10" t="s"/>
+    </x:row>
+    <x:row r="120" hidden="0">
+      <x:c r="A120">
+        <x:v>135</x:v>
+      </x:c>
+      <x:c r="B120" s="2">
+        <x:v>46223.49759259259</x:v>
+      </x:c>
+      <x:c r="C120" s="2">
+        <x:v>46223.49793981481</x:v>
+      </x:c>
+      <x:c r="D120" s="10" t="s">
+        <x:v>70</x:v>
+      </x:c>
+      <x:c r="E120" s="10" t="s">
+        <x:v>71</x:v>
+      </x:c>
+      <x:c r="F120" s="2"/>
+      <x:c r="G120" s="3">
+        <x:v>46224</x:v>
+      </x:c>
+      <x:c r="H120" s="10" t="s">
+        <x:v>18</x:v>
+      </x:c>
+      <x:c r="I120" s="10" t="s">
+        <x:v>71</x:v>
+      </x:c>
+      <x:c r="J120" s="10" t="s"/>
+      <x:c r="K120" s="10" t="s"/>
+      <x:c r="L120" s="10" t="s"/>
+    </x:row>
+    <x:row r="121" hidden="0">
+      <x:c r="A121">
+        <x:v>136</x:v>
+      </x:c>
+      <x:c r="B121" s="2">
+        <x:v>46223.503645833334</x:v>
+      </x:c>
+      <x:c r="C121" s="2">
+        <x:v>46223.50407407407</x:v>
+      </x:c>
+      <x:c r="D121" s="10" t="s">
+        <x:v>23</x:v>
+      </x:c>
+      <x:c r="E121" s="10" t="s">
+        <x:v>24</x:v>
+      </x:c>
+      <x:c r="F121" s="2"/>
+      <x:c r="G121" s="3">
+        <x:v>46224</x:v>
+      </x:c>
+      <x:c r="H121" s="10" t="s">
+        <x:v>18</x:v>
+      </x:c>
+      <x:c r="I121" s="10" t="s">
+        <x:v>75</x:v>
+      </x:c>
+      <x:c r="J121" s="10" t="s"/>
+      <x:c r="K121" s="10" t="s"/>
+      <x:c r="L121" s="10" t="s"/>
+    </x:row>
+    <x:row r="122" hidden="0">
+      <x:c r="A122">
+        <x:v>137</x:v>
+      </x:c>
+      <x:c r="B122" s="2">
+        <x:v>46223.54880787037</x:v>
+      </x:c>
+      <x:c r="C122" s="2">
+        <x:v>46223.548993055556</x:v>
+      </x:c>
+      <x:c r="D122" s="10" t="s">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="E122" s="10" t="s">
+        <x:v>21</x:v>
+      </x:c>
+      <x:c r="F122" s="2"/>
+      <x:c r="G122" s="3">
+        <x:v>46224</x:v>
+      </x:c>
+      <x:c r="H122" s="10" t="s">
+        <x:v>18</x:v>
+      </x:c>
+      <x:c r="I122" s="10" t="s">
+        <x:v>19</x:v>
+      </x:c>
+      <x:c r="J122" s="10" t="s"/>
+      <x:c r="K122" s="10" t="s"/>
+      <x:c r="L122" s="10" t="s"/>
+    </x:row>
+    <x:row r="123" hidden="0">
+      <x:c r="A123">
+        <x:v>138</x:v>
+      </x:c>
+      <x:c r="B123" s="2">
+        <x:v>46223.57087962963</x:v>
+      </x:c>
+      <x:c r="C123" s="2">
+        <x:v>46223.57104166667</x:v>
+      </x:c>
+      <x:c r="D123" s="10" t="s">
+        <x:v>28</x:v>
+      </x:c>
+      <x:c r="E123" s="10" t="s">
+        <x:v>29</x:v>
+      </x:c>
+      <x:c r="F123" s="2"/>
+      <x:c r="G123" s="3">
+        <x:v>46224</x:v>
+      </x:c>
+      <x:c r="H123" s="10" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="I123" s="10" t="s"/>
+      <x:c r="J123" s="10" t="s"/>
+      <x:c r="K123" s="10" t="s"/>
+      <x:c r="L123" s="10" t="s">
+        <x:v>27</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="124" hidden="0">
+      <x:c r="A124">
+        <x:v>139</x:v>
+      </x:c>
+      <x:c r="B124" s="2">
+        <x:v>46224.395324074074</x:v>
+      </x:c>
+      <x:c r="C124" s="2">
+        <x:v>46224.395462962966</x:v>
+      </x:c>
+      <x:c r="D124" s="10" t="s">
+        <x:v>72</x:v>
+      </x:c>
+      <x:c r="E124" s="10" t="s">
+        <x:v>73</x:v>
+      </x:c>
+      <x:c r="F124" s="2"/>
+      <x:c r="G124" s="3">
+        <x:v>46225</x:v>
+      </x:c>
+      <x:c r="H124" s="10" t="s">
+        <x:v>18</x:v>
+      </x:c>
+      <x:c r="I124" s="10" t="s">
+        <x:v>73</x:v>
+      </x:c>
+      <x:c r="J124" s="10" t="s"/>
+      <x:c r="K124" s="10" t="s"/>
+      <x:c r="L124" s="10" t="s"/>
+    </x:row>
+    <x:row r="125" hidden="0">
+      <x:c r="A125">
+        <x:v>140</x:v>
+      </x:c>
+      <x:c r="B125" s="2">
+        <x:v>46224.60273148148</x:v>
+      </x:c>
+      <x:c r="C125" s="2">
+        <x:v>46224.60283564815</x:v>
+      </x:c>
+      <x:c r="D125" s="10" t="s">
+        <x:v>23</x:v>
+      </x:c>
+      <x:c r="E125" s="10" t="s">
+        <x:v>24</x:v>
+      </x:c>
+      <x:c r="F125" s="2"/>
+      <x:c r="G125" s="3">
+        <x:v>46225</x:v>
+      </x:c>
+      <x:c r="H125" s="10" t="s">
+        <x:v>18</x:v>
+      </x:c>
+      <x:c r="I125" s="10" t="s">
+        <x:v>73</x:v>
+      </x:c>
+      <x:c r="J125" s="10" t="s"/>
+      <x:c r="K125" s="10" t="s"/>
+      <x:c r="L125" s="10" t="s"/>
+    </x:row>
+    <x:row r="126" hidden="0">
+      <x:c r="A126">
+        <x:v>141</x:v>
+      </x:c>
+      <x:c r="B126" s="2">
+        <x:v>46224.60302083333</x:v>
+      </x:c>
+      <x:c r="C126" s="2">
+        <x:v>46224.60344907407</x:v>
+      </x:c>
+      <x:c r="D126" s="10" t="s">
+        <x:v>33</x:v>
+      </x:c>
+      <x:c r="E126" s="10" t="s">
+        <x:v>34</x:v>
+      </x:c>
+      <x:c r="F126" s="2"/>
+      <x:c r="G126" s="3">
+        <x:v>46225</x:v>
+      </x:c>
+      <x:c r="H126" s="10" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="I126" s="10" t="s"/>
+      <x:c r="J126" s="10" t="s"/>
+      <x:c r="K126" s="10" t="s"/>
+      <x:c r="L126" s="10" t="s">
+        <x:v>26</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="127" hidden="0">
+      <x:c r="A127">
+        <x:v>142</x:v>
+      </x:c>
+      <x:c r="B127" s="2">
+        <x:v>46224.60309027778</x:v>
+      </x:c>
+      <x:c r="C127" s="2">
+        <x:v>46224.604097222225</x:v>
+      </x:c>
+      <x:c r="D127" s="10" t="s">
+        <x:v>35</x:v>
+      </x:c>
+      <x:c r="E127" s="10" t="s">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="F127" s="2"/>
+      <x:c r="G127" s="3">
+        <x:v>46225</x:v>
+      </x:c>
+      <x:c r="H127" s="10" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="I127" s="10" t="s"/>
+      <x:c r="J127" s="10" t="s"/>
+      <x:c r="K127" s="10" t="s"/>
+      <x:c r="L127" s="10" t="s">
+        <x:v>26</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="128" hidden="0">
+      <x:c r="A128">
+        <x:v>143</x:v>
+      </x:c>
+      <x:c r="B128" s="2">
+        <x:v>46224.60408564815</x:v>
+      </x:c>
+      <x:c r="C128" s="2">
+        <x:v>46224.60424768519</x:v>
+      </x:c>
+      <x:c r="D128" s="10" t="s">
+        <x:v>70</x:v>
+      </x:c>
+      <x:c r="E128" s="10" t="s">
+        <x:v>71</x:v>
+      </x:c>
+      <x:c r="F128" s="2"/>
+      <x:c r="G128" s="3">
+        <x:v>46225</x:v>
+      </x:c>
+      <x:c r="H128" s="10" t="s">
+        <x:v>18</x:v>
+      </x:c>
+      <x:c r="I128" s="10" t="s">
+        <x:v>73</x:v>
+      </x:c>
+      <x:c r="J128" s="10" t="s"/>
+      <x:c r="K128" s="10" t="s"/>
+      <x:c r="L128" s="10" t="s"/>
+    </x:row>
+    <x:row r="129" hidden="0">
+      <x:c r="A129">
+        <x:v>144</x:v>
+      </x:c>
+      <x:c r="B129" s="2">
+        <x:v>46224.604537037034</x:v>
+      </x:c>
+      <x:c r="C129" s="2">
+        <x:v>46224.60474537037</x:v>
+      </x:c>
+      <x:c r="D129" s="10" t="s">
+        <x:v>60</x:v>
+      </x:c>
+      <x:c r="E129" s="10" t="s">
+        <x:v>61</x:v>
+      </x:c>
+      <x:c r="F129" s="2"/>
+      <x:c r="G129" s="3">
+        <x:v>46225</x:v>
+      </x:c>
+      <x:c r="H129" s="10" t="s">
+        <x:v>18</x:v>
+      </x:c>
+      <x:c r="I129" s="10" t="s">
+        <x:v>21</x:v>
+      </x:c>
+      <x:c r="J129" s="10" t="s"/>
+      <x:c r="K129" s="10" t="s"/>
+      <x:c r="L129" s="10" t="s"/>
+    </x:row>
+    <x:row r="130" hidden="0">
+      <x:c r="A130">
+        <x:v>145</x:v>
+      </x:c>
+      <x:c r="B130" s="2">
+        <x:v>46224.60459490741</x:v>
+      </x:c>
+      <x:c r="C130" s="2">
+        <x:v>46224.60488425926</x:v>
+      </x:c>
+      <x:c r="D130" s="10" t="s">
+        <x:v>48</x:v>
+      </x:c>
+      <x:c r="E130" s="10" t="s">
+        <x:v>27</x:v>
+      </x:c>
+      <x:c r="F130" s="2"/>
+      <x:c r="G130" s="3">
+        <x:v>46225</x:v>
+      </x:c>
+      <x:c r="H130" s="10" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="I130" s="10" t="s"/>
+      <x:c r="J130" s="10" t="s"/>
+      <x:c r="K130" s="10" t="s"/>
+      <x:c r="L130" s="10" t="s">
+        <x:v>26</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="131" hidden="0">
+      <x:c r="A131">
+        <x:v>146</x:v>
+      </x:c>
+      <x:c r="B131" s="2">
+        <x:v>46224.60487268519</x:v>
+      </x:c>
+      <x:c r="C131" s="2">
+        <x:v>46224.60502314815</x:v>
+      </x:c>
+      <x:c r="D131" s="10" t="s">
+        <x:v>31</x:v>
+      </x:c>
+      <x:c r="E131" s="10" t="s">
+        <x:v>32</x:v>
+      </x:c>
+      <x:c r="F131" s="2"/>
+      <x:c r="G131" s="3">
+        <x:v>46225</x:v>
+      </x:c>
+      <x:c r="H131" s="10" t="s">
+        <x:v>18</x:v>
+      </x:c>
+      <x:c r="I131" s="10" t="s">
+        <x:v>21</x:v>
+      </x:c>
+      <x:c r="J131" s="10" t="s"/>
+      <x:c r="K131" s="10" t="s"/>
+      <x:c r="L131" s="10" t="s"/>
+    </x:row>
+    <x:row r="132" hidden="0">
+      <x:c r="A132">
+        <x:v>147</x:v>
+      </x:c>
+      <x:c r="B132" s="2">
+        <x:v>46224.604791666665</x:v>
+      </x:c>
+      <x:c r="C132" s="2">
+        <x:v>46224.605208333334</x:v>
+      </x:c>
+      <x:c r="D132" s="10" t="s">
+        <x:v>36</x:v>
+      </x:c>
+      <x:c r="E132" s="10" t="s">
+        <x:v>37</x:v>
+      </x:c>
+      <x:c r="F132" s="2"/>
+      <x:c r="G132" s="3">
+        <x:v>46225</x:v>
+      </x:c>
+      <x:c r="H132" s="10" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="I132" s="10" t="s"/>
+      <x:c r="J132" s="10" t="s"/>
+      <x:c r="K132" s="10" t="s"/>
+      <x:c r="L132" s="10" t="s">
+        <x:v>15</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="133" hidden="0">
+      <x:c r="A133">
+        <x:v>148</x:v>
+      </x:c>
+      <x:c r="B133" s="2">
+        <x:v>46224.60581018519</x:v>
+      </x:c>
+      <x:c r="C133" s="2">
+        <x:v>46224.60592592593</x:v>
+      </x:c>
+      <x:c r="D133" s="10" t="s">
+        <x:v>38</x:v>
+      </x:c>
+      <x:c r="E133" s="10" t="s">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="F133" s="2"/>
+      <x:c r="G133" s="3">
+        <x:v>46225</x:v>
+      </x:c>
+      <x:c r="H133" s="10" t="s">
+        <x:v>18</x:v>
+      </x:c>
+      <x:c r="I133" s="10" t="s">
+        <x:v>73</x:v>
+      </x:c>
+      <x:c r="J133" s="10" t="s"/>
+      <x:c r="K133" s="10" t="s"/>
+      <x:c r="L133" s="10" t="s"/>
+    </x:row>
+    <x:row r="134" hidden="0">
+      <x:c r="A134">
+        <x:v>149</x:v>
+      </x:c>
+      <x:c r="B134" s="2">
+        <x:v>46224.61449074074</x:v>
+      </x:c>
+      <x:c r="C134" s="2">
+        <x:v>46224.614699074074</x:v>
+      </x:c>
+      <x:c r="D134" s="10" t="s">
+        <x:v>28</x:v>
+      </x:c>
+      <x:c r="E134" s="10" t="s">
+        <x:v>29</x:v>
+      </x:c>
+      <x:c r="F134" s="2"/>
+      <x:c r="G134" s="3">
+        <x:v>46225</x:v>
+      </x:c>
+      <x:c r="H134" s="10" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="I134" s="10" t="s"/>
+      <x:c r="J134" s="10" t="s"/>
+      <x:c r="K134" s="10" t="s"/>
+      <x:c r="L134" s="10" t="s">
+        <x:v>87</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="135" hidden="0">
+      <x:c r="A135">
+        <x:v>150</x:v>
+      </x:c>
+      <x:c r="B135" s="2">
+        <x:v>46224.61550925926</x:v>
+      </x:c>
+      <x:c r="C135" s="2">
+        <x:v>46224.615636574075</x:v>
+      </x:c>
+      <x:c r="D135" s="10" t="s">
+        <x:v>12</x:v>
+      </x:c>
+      <x:c r="E135" s="10" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="F135" s="2"/>
+      <x:c r="G135" s="3">
+        <x:v>46225</x:v>
+      </x:c>
+      <x:c r="H135" s="10" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="I135" s="10" t="s"/>
+      <x:c r="J135" s="10" t="s"/>
+      <x:c r="K135" s="10" t="s"/>
+      <x:c r="L135" s="10" t="s">
+        <x:v>26</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="136" hidden="0">
+      <x:c r="A136">
+        <x:v>151</x:v>
+      </x:c>
+      <x:c r="B136" s="2">
+        <x:v>46225.65255787037</x:v>
+      </x:c>
+      <x:c r="C136" s="2">
+        <x:v>46225.65269675926</x:v>
+      </x:c>
+      <x:c r="D136" s="10" t="s">
+        <x:v>12</x:v>
+      </x:c>
+      <x:c r="E136" s="10" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="F136" s="2"/>
+      <x:c r="G136" s="3">
+        <x:v>46226</x:v>
+      </x:c>
+      <x:c r="H136" s="10" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="I136" s="10" t="s"/>
+      <x:c r="J136" s="10" t="s"/>
+      <x:c r="K136" s="10" t="s"/>
+      <x:c r="L136" s="10" t="s">
+        <x:v>26</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="137" hidden="0">
+      <x:c r="A137">
+        <x:v>152</x:v>
+      </x:c>
+      <x:c r="B137" s="2">
+        <x:v>46225.65269675926</x:v>
+      </x:c>
+      <x:c r="C137" s="2">
+        <x:v>46225.65287037037</x:v>
+      </x:c>
+      <x:c r="D137" s="10" t="s">
+        <x:v>23</x:v>
+      </x:c>
+      <x:c r="E137" s="10" t="s">
+        <x:v>24</x:v>
+      </x:c>
+      <x:c r="F137" s="2"/>
+      <x:c r="G137" s="3">
+        <x:v>46226</x:v>
+      </x:c>
+      <x:c r="H137" s="10" t="s">
+        <x:v>18</x:v>
+      </x:c>
+      <x:c r="I137" s="10" t="s">
+        <x:v>19</x:v>
+      </x:c>
+      <x:c r="J137" s="10" t="s"/>
+      <x:c r="K137" s="10" t="s"/>
+      <x:c r="L137" s="10" t="s"/>
+    </x:row>
+    <x:row r="138" hidden="0">
+      <x:c r="A138">
+        <x:v>153</x:v>
+      </x:c>
+      <x:c r="B138" s="2">
+        <x:v>46225.652407407404</x:v>
+      </x:c>
+      <x:c r="C138" s="2">
+        <x:v>46225.65290509259</x:v>
+      </x:c>
+      <x:c r="D138" s="10" t="s">
+        <x:v>72</x:v>
+      </x:c>
+      <x:c r="E138" s="10" t="s">
+        <x:v>73</x:v>
+      </x:c>
+      <x:c r="F138" s="2"/>
+      <x:c r="G138" s="3">
+        <x:v>46226</x:v>
+      </x:c>
+      <x:c r="H138" s="10" t="s">
+        <x:v>18</x:v>
+      </x:c>
+      <x:c r="I138" s="10" t="s">
+        <x:v>73</x:v>
+      </x:c>
+      <x:c r="J138" s="10" t="s"/>
+      <x:c r="K138" s="10" t="s"/>
+      <x:c r="L138" s="10" t="s"/>
+    </x:row>
+    <x:row r="139" hidden="0">
+      <x:c r="A139">
+        <x:v>154</x:v>
+      </x:c>
+      <x:c r="B139" s="2">
+        <x:v>46225.667349537034</x:v>
+      </x:c>
+      <x:c r="C139" s="2">
+        <x:v>46225.667604166665</x:v>
+      </x:c>
+      <x:c r="D139" s="10" t="s">
+        <x:v>46</x:v>
+      </x:c>
+      <x:c r="E139" s="10" t="s">
+        <x:v>47</x:v>
+      </x:c>
+      <x:c r="F139" s="2"/>
+      <x:c r="G139" s="3">
+        <x:v>46226</x:v>
+      </x:c>
+      <x:c r="H139" s="10" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="I139" s="10" t="s"/>
+      <x:c r="J139" s="10" t="s"/>
+      <x:c r="K139" s="10" t="s"/>
+      <x:c r="L139" s="10" t="s">
+        <x:v>27</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="140" hidden="0">
+      <x:c r="A140">
+        <x:v>155</x:v>
+      </x:c>
+      <x:c r="B140" s="2">
+        <x:v>46226.249930555554</x:v>
+      </x:c>
+      <x:c r="C140" s="2">
+        <x:v>46226.250069444446</x:v>
+      </x:c>
+      <x:c r="D140" s="10" t="s">
+        <x:v>70</x:v>
+      </x:c>
+      <x:c r="E140" s="10" t="s">
+        <x:v>71</x:v>
+      </x:c>
+      <x:c r="F140" s="2"/>
+      <x:c r="G140" s="3">
+        <x:v>46226</x:v>
+      </x:c>
+      <x:c r="H140" s="10" t="s">
+        <x:v>18</x:v>
+      </x:c>
+      <x:c r="I140" s="10" t="s">
+        <x:v>75</x:v>
+      </x:c>
+      <x:c r="J140" s="10" t="s"/>
+      <x:c r="K140" s="10" t="s"/>
+      <x:c r="L140" s="10" t="s"/>
+    </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
   <x:tableParts count="1">
-    <x:tablePart r:id="Rb634b10b57a74da8"/>
+    <x:tablePart r:id="R06ff57612a85454c"/>
   </x:tableParts>
 </x:worksheet>
 </file>